--- a/Working files/Rating-Agencies/Working Tables-Feb2026.xlsx
+++ b/Working files/Rating-Agencies/Working Tables-Feb2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\MINECOFIN\Macro\Rating Agencies\S&amp;P\2025\October\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\GitHub\MISC\Working files\Rating-Agencies\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{439EB866-2155-43AE-B35E-8D21DDD7903C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAF737CE-C0B8-4495-8DE5-87323E5DB5EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" activeTab="4" xr2:uid="{BFCAC876-2B89-4281-95D3-F76E7D27FE8F}"/>
+    <workbookView xWindow="-28920" yWindow="2025" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{BFCAC876-2B89-4281-95D3-F76E7D27FE8F}"/>
   </bookViews>
   <sheets>
     <sheet name="HFIs" sheetId="2" r:id="rId1"/>
@@ -1793,6 +1793,26 @@
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="7" applyFont="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="43" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="6" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="12" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="13" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="14" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="15" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="12" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1808,25 +1828,7 @@
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="6" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="14" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="12" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="13" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="14" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="15" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1853,8 +1855,6 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="8">
     <cellStyle name="Comma" xfId="7" builtinId="3"/>
@@ -14577,48 +14577,48 @@
   <sheetData>
     <row r="2" spans="5:29" ht="15.5" thickBot="1" x14ac:dyDescent="0.9"/>
     <row r="3" spans="5:29" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
-      <c r="E3" s="160"/>
+      <c r="E3" s="157"/>
       <c r="F3" s="84">
         <v>2023</v>
       </c>
-      <c r="G3" s="163">
+      <c r="G3" s="159">
         <v>2024</v>
       </c>
-      <c r="H3" s="164"/>
-      <c r="I3" s="164"/>
-      <c r="J3" s="165"/>
-      <c r="K3" s="163">
+      <c r="H3" s="160"/>
+      <c r="I3" s="160"/>
+      <c r="J3" s="161"/>
+      <c r="K3" s="159">
         <v>2025</v>
       </c>
-      <c r="L3" s="164"/>
-      <c r="M3" s="164"/>
-      <c r="N3" s="166"/>
+      <c r="L3" s="160"/>
+      <c r="M3" s="160"/>
+      <c r="N3" s="162"/>
       <c r="O3" s="83">
         <v>2024</v>
       </c>
       <c r="P3" s="83">
         <v>2025</v>
       </c>
-      <c r="Q3" s="160"/>
+      <c r="Q3" s="157"/>
       <c r="R3" s="85">
         <v>2024</v>
       </c>
-      <c r="S3" s="155">
+      <c r="S3" s="163">
         <v>2025</v>
       </c>
-      <c r="T3" s="156"/>
-      <c r="U3" s="156"/>
-      <c r="V3" s="157"/>
-      <c r="Y3" s="160"/>
-      <c r="Z3" s="155">
+      <c r="T3" s="164"/>
+      <c r="U3" s="164"/>
+      <c r="V3" s="165"/>
+      <c r="Y3" s="157"/>
+      <c r="Z3" s="163">
         <v>2025</v>
       </c>
-      <c r="AA3" s="156"/>
-      <c r="AB3" s="156"/>
-      <c r="AC3" s="157"/>
+      <c r="AA3" s="164"/>
+      <c r="AB3" s="164"/>
+      <c r="AC3" s="165"/>
     </row>
     <row r="4" spans="5:29" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
-      <c r="E4" s="161"/>
+      <c r="E4" s="158"/>
       <c r="F4" s="86" t="s">
         <v>171</v>
       </c>
@@ -14652,7 +14652,7 @@
       <c r="P4" s="83" t="s">
         <v>174</v>
       </c>
-      <c r="Q4" s="161"/>
+      <c r="Q4" s="158"/>
       <c r="R4" s="89" t="s">
         <v>174</v>
       </c>
@@ -14668,7 +14668,7 @@
       <c r="V4" s="92" t="s">
         <v>176</v>
       </c>
-      <c r="Y4" s="161"/>
+      <c r="Y4" s="158"/>
       <c r="Z4" s="90" t="s">
         <v>161</v>
       </c>
@@ -15640,41 +15640,41 @@
       </c>
     </row>
     <row r="16" spans="5:29" x14ac:dyDescent="0.75">
-      <c r="Q16" s="158" t="s">
+      <c r="Q16" s="166" t="s">
         <v>188</v>
       </c>
-      <c r="R16" s="158"/>
-      <c r="S16" s="158"/>
-      <c r="T16" s="158"/>
-      <c r="U16" s="158"/>
-      <c r="V16" s="158"/>
+      <c r="R16" s="166"/>
+      <c r="S16" s="166"/>
+      <c r="T16" s="166"/>
+      <c r="U16" s="166"/>
+      <c r="V16" s="166"/>
     </row>
     <row r="17" spans="17:22" x14ac:dyDescent="0.75">
-      <c r="Q17" s="159" t="s">
+      <c r="Q17" s="167" t="s">
         <v>189</v>
       </c>
-      <c r="R17" s="159"/>
-      <c r="S17" s="159"/>
-      <c r="T17" s="159"/>
-      <c r="U17" s="159"/>
-      <c r="V17" s="159"/>
+      <c r="R17" s="167"/>
+      <c r="S17" s="167"/>
+      <c r="T17" s="167"/>
+      <c r="U17" s="167"/>
+      <c r="V17" s="167"/>
     </row>
     <row r="19" spans="17:22" ht="15.5" thickBot="1" x14ac:dyDescent="0.9"/>
     <row r="20" spans="17:22" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
-      <c r="Q20" s="160" t="s">
+      <c r="Q20" s="157" t="s">
         <v>190</v>
       </c>
-      <c r="R20" s="155">
+      <c r="R20" s="163">
         <v>2024</v>
       </c>
-      <c r="S20" s="162"/>
-      <c r="T20" s="155">
+      <c r="S20" s="168"/>
+      <c r="T20" s="163">
         <v>2025</v>
       </c>
-      <c r="U20" s="157"/>
+      <c r="U20" s="165"/>
     </row>
     <row r="21" spans="17:22" ht="15.5" thickBot="1" x14ac:dyDescent="0.9">
-      <c r="Q21" s="161"/>
+      <c r="Q21" s="158"/>
       <c r="R21" s="89" t="s">
         <v>191</v>
       </c>
@@ -15910,11 +15910,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="G3:J3"/>
-    <mergeCell ref="K3:N3"/>
-    <mergeCell ref="Q3:Q4"/>
-    <mergeCell ref="S3:V3"/>
     <mergeCell ref="Z3:AC3"/>
     <mergeCell ref="Q16:V16"/>
     <mergeCell ref="Q17:V17"/>
@@ -15922,6 +15917,11 @@
     <mergeCell ref="R20:S20"/>
     <mergeCell ref="T20:U20"/>
     <mergeCell ref="Y3:Y4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="K3:N3"/>
+    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="S3:V3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -16341,11 +16341,11 @@
       <c r="CC6" s="22"/>
       <c r="CD6" s="22"/>
       <c r="CE6" s="22"/>
-      <c r="CF6" s="169" t="s">
+      <c r="CF6" s="171" t="s">
         <v>84</v>
       </c>
-      <c r="CG6" s="169"/>
-      <c r="CH6" s="169"/>
+      <c r="CG6" s="171"/>
+      <c r="CH6" s="171"/>
       <c r="CI6" s="19"/>
       <c r="CJ6" s="19"/>
       <c r="CK6" s="19"/>
@@ -26196,13 +26196,13 @@
     </row>
     <row r="50" spans="1:85" ht="17.75" x14ac:dyDescent="0.75">
       <c r="A50" s="1"/>
-      <c r="C50" s="170" t="s">
+      <c r="C50" s="172" t="s">
         <v>159</v>
       </c>
-      <c r="D50" s="172">
+      <c r="D50" s="174">
         <v>2025</v>
       </c>
-      <c r="E50" s="173"/>
+      <c r="E50" s="175"/>
       <c r="AX50" s="49">
         <v>2017</v>
       </c>
@@ -26233,7 +26233,7 @@
     </row>
     <row r="51" spans="1:85" ht="18.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A51" s="1"/>
-      <c r="C51" s="171"/>
+      <c r="C51" s="173"/>
       <c r="D51" s="50" t="s">
         <v>161</v>
       </c>
@@ -26283,10 +26283,10 @@
       <c r="AR51" s="52"/>
       <c r="AS51" s="52"/>
       <c r="AT51" s="52"/>
-      <c r="AU51" s="174" t="s">
+      <c r="AU51" s="176" t="s">
         <v>162</v>
       </c>
-      <c r="AV51" s="168" t="s">
+      <c r="AV51" s="170" t="s">
         <v>163</v>
       </c>
       <c r="AW51" s="52" t="s">
@@ -26413,8 +26413,8 @@
       <c r="AR52" s="58"/>
       <c r="AS52" s="58"/>
       <c r="AT52" s="58"/>
-      <c r="AU52" s="174"/>
-      <c r="AV52" s="168"/>
+      <c r="AU52" s="176"/>
+      <c r="AV52" s="170"/>
       <c r="AW52" s="58" t="s">
         <v>165</v>
       </c>
@@ -26476,8 +26476,8 @@
       <c r="C53" s="59"/>
       <c r="D53" s="22"/>
       <c r="E53" s="60"/>
-      <c r="AU53" s="174"/>
-      <c r="AV53" s="168"/>
+      <c r="AU53" s="176"/>
+      <c r="AV53" s="170"/>
       <c r="AW53" s="61" t="s">
         <v>166</v>
       </c>
@@ -26531,10 +26531,10 @@
         <f>CE9</f>
         <v>0.1</v>
       </c>
-      <c r="AU54" s="167" t="s">
+      <c r="AU54" s="169" t="s">
         <v>167</v>
       </c>
-      <c r="AV54" s="168" t="s">
+      <c r="AV54" s="170" t="s">
         <v>168</v>
       </c>
       <c r="AW54" s="28" t="s">
@@ -26590,8 +26590,8 @@
         <f t="shared" ref="E55" si="5">CH10</f>
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="AU55" s="167"/>
-      <c r="AV55" s="168"/>
+      <c r="AU55" s="169"/>
+      <c r="AV55" s="170"/>
       <c r="AW55" s="28" t="s">
         <v>170</v>
       </c>
@@ -26633,7 +26633,7 @@
         <f>CH11</f>
         <v>0.215</v>
       </c>
-      <c r="AV56" s="168"/>
+      <c r="AV56" s="170"/>
       <c r="AW56" s="61" t="s">
         <v>166</v>
       </c>
@@ -27398,7 +27398,7 @@
         <v>4088.9526285563329</v>
       </c>
       <c r="H6">
-        <f t="shared" ref="H6:H38" si="0">G6/G5-1</f>
+        <f t="shared" ref="H6:H37" si="0">G6/G5-1</f>
         <v>8.1220292485233436E-2</v>
       </c>
       <c r="K6" s="115"/>
@@ -29672,7 +29672,7 @@
       <c r="C107" s="125">
         <v>11882.042086161728</v>
       </c>
-      <c r="D107" s="175">
+      <c r="D107" s="155">
         <v>11882.042086161728</v>
       </c>
       <c r="E107" s="119"/>
@@ -29684,7 +29684,7 @@
       <c r="C108" s="125">
         <v>12104.034347454632</v>
       </c>
-      <c r="D108" s="175">
+      <c r="D108" s="155">
         <v>12104.034347454632</v>
       </c>
       <c r="E108" s="119"/>
@@ -29693,7 +29693,7 @@
       <c r="B109" s="124">
         <v>45992</v>
       </c>
-      <c r="C109" s="176">
+      <c r="C109" s="156">
         <f>AVERAGE(C107:C108)</f>
         <v>11993.03821680818</v>
       </c>
@@ -31485,7 +31485,7 @@
       </c>
     </row>
     <row r="109" spans="2:4" x14ac:dyDescent="0.75">
-      <c r="C109" s="176">
+      <c r="C109" s="156">
         <f>AVERAGE(C107:C108)</f>
         <v>253.7649635522227</v>
       </c>
